--- a/data/gravel/3T Racemax Italia 2025.xlsx
+++ b/data/gravel/3T Racemax Italia 2025.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{741ADB4B-B133-2F47-A61C-B0C6BF380A4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8539556-B1B3-F042-A548-629309E2C072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3880" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="105">
   <si>
     <t>brand</t>
   </si>
@@ -330,6 +330,24 @@
   </si>
   <si>
     <t>a8:f32</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>gravel</t>
+  </si>
+  <si>
+    <t>handlebar</t>
+  </si>
+  <si>
+    <t>drop bar</t>
+  </si>
+  <si>
+    <t>fork</t>
+  </si>
+  <si>
+    <t>rigid</t>
   </si>
 </sst>
 </file>
@@ -682,7 +700,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1172,10 +1190,10 @@
     </row>
     <row r="35" spans="1:7" ht="21">
       <c r="A35" t="s">
-        <v>31</v>
+        <v>99</v>
       </c>
       <c r="B35" t="s">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>68</v>
@@ -1195,10 +1213,10 @@
     </row>
     <row r="36" spans="1:7" ht="21">
       <c r="A36" t="s">
-        <v>33</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>93</v>
+        <v>101</v>
+      </c>
+      <c r="B36" t="s">
+        <v>102</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>73</v>
@@ -1218,196 +1236,220 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>34</v>
+        <v>103</v>
+      </c>
+      <c r="B37" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>35</v>
-      </c>
-      <c r="B38">
-        <v>46</v>
+        <v>31</v>
+      </c>
+      <c r="B38" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>36</v>
-      </c>
-      <c r="B39">
-        <v>2.4</v>
+        <v>33</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>38</v>
+        <v>35</v>
+      </c>
+      <c r="B41">
+        <v>46</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="B42">
+        <v>2.4</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>43</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>49</v>
+        <v>46</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>56</v>
-      </c>
-      <c r="B59">
-        <v>2</v>
+        <v>53</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>57</v>
-      </c>
-      <c r="B60">
-        <v>1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>58</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>93</v>
+        <v>55</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>59</v>
+        <v>56</v>
+      </c>
+      <c r="B62">
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>60</v>
+        <v>57</v>
+      </c>
+      <c r="B63">
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>61</v>
+        <v>58</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>63</v>
-      </c>
-      <c r="B66">
-        <v>6399</v>
+        <v>60</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>64</v>
-      </c>
-      <c r="B67">
-        <v>8499</v>
+        <v>61</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
+        <v>63</v>
+      </c>
+      <c r="B69">
+        <v>6399</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" t="s">
+        <v>64</v>
+      </c>
+      <c r="B70">
+        <v>8499</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" t="s">
         <v>66</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B72" s="1" t="s">
         <v>96</v>
       </c>
     </row>

--- a/data/gravel/3T Racemax Italia 2025.xlsx
+++ b/data/gravel/3T Racemax Italia 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8539556-B1B3-F042-A548-629309E2C072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C6EF7CC-D316-274A-A94A-8ABAB3677F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3880" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="106">
   <si>
     <t>brand</t>
   </si>
@@ -348,6 +348,9 @@
   </si>
   <si>
     <t>rigid</t>
+  </si>
+  <si>
+    <t>https://us.3t.bike/cdn/shop/files/Extrema---Project-X-1520-HDR-Modifica_460x.jpg?v=1759848488</t>
   </si>
 </sst>
 </file>
@@ -746,6 +749,11 @@
         <v>92</v>
       </c>
     </row>
+    <row r="6" spans="1:6">
+      <c r="B6" t="s">
+        <v>105</v>
+      </c>
+    </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>5</v>

--- a/data/gravel/3T Racemax Italia 2025.xlsx
+++ b/data/gravel/3T Racemax Italia 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C6EF7CC-D316-274A-A94A-8ABAB3677F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A06B1D6-852E-E44B-8708-C423D23C4B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3880" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="108">
   <si>
     <t>brand</t>
   </si>
@@ -323,9 +323,6 @@
     <t>threaded</t>
   </si>
   <si>
-    <t>us</t>
-  </si>
-  <si>
     <t>frame_weight</t>
   </si>
   <si>
@@ -351,6 +348,15 @@
   </si>
   <si>
     <t>https://us.3t.bike/cdn/shop/files/Extrema---Project-X-1520-HDR-Modifica_460x.jpg?v=1759848488</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Bergamo, Italy</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -703,7 +709,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -751,7 +757,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="B6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -759,7 +765,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="21">
@@ -1039,7 +1045,7 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1198,10 +1204,10 @@
     </row>
     <row r="35" spans="1:7" ht="21">
       <c r="A35" t="s">
+        <v>98</v>
+      </c>
+      <c r="B35" t="s">
         <v>99</v>
-      </c>
-      <c r="B35" t="s">
-        <v>100</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>68</v>
@@ -1221,10 +1227,10 @@
     </row>
     <row r="36" spans="1:7" ht="21">
       <c r="A36" t="s">
+        <v>100</v>
+      </c>
+      <c r="B36" t="s">
         <v>101</v>
-      </c>
-      <c r="B36" t="s">
-        <v>102</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>73</v>
@@ -1244,10 +1250,10 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
+        <v>102</v>
+      </c>
+      <c r="B37" t="s">
         <v>103</v>
-      </c>
-      <c r="B37" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1458,7 +1464,15 @@
         <v>66</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>96</v>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
+        <v>105</v>
+      </c>
+      <c r="B73" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/3T Racemax Italia 2025.xlsx
+++ b/data/gravel/3T Racemax Italia 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A06B1D6-852E-E44B-8708-C423D23C4B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{222BA354-D58A-D748-BB88-32415E8C0937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3880" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="109">
   <si>
     <t>brand</t>
   </si>
@@ -357,6 +357,9 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>no</t>
   </si>
 </sst>
 </file>
@@ -1383,6 +1386,9 @@
       <c r="A59" t="s">
         <v>53</v>
       </c>
+      <c r="B59" s="1" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">

--- a/data/gravel/3T Racemax Italia 2025.xlsx
+++ b/data/gravel/3T Racemax Italia 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{222BA354-D58A-D748-BB88-32415E8C0937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{735E28CF-BC39-9844-881F-1C83BF600AC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3880" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="115">
   <si>
     <t>brand</t>
   </si>
@@ -360,6 +360,24 @@
   </si>
   <si>
     <t>no</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -712,7 +730,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1328,156 +1346,186 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>44</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>45</v>
+        <v>111</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>46</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>47</v>
+        <v>113</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>48</v>
+        <v>114</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>43</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>52</v>
+        <v>46</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>53</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>108</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>56</v>
-      </c>
-      <c r="B62">
-        <v>2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>57</v>
-      </c>
-      <c r="B63">
-        <v>1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>58</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>93</v>
+        <v>52</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>59</v>
+        <v>53</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>62</v>
+        <v>56</v>
+      </c>
+      <c r="B68">
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B69">
-        <v>6399</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>64</v>
-      </c>
-      <c r="B70">
-        <v>8499</v>
+        <v>58</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>66</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>107</v>
+        <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>63</v>
+      </c>
+      <c r="B75">
+        <v>6399</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>64</v>
+      </c>
+      <c r="B76">
+        <v>8499</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>66</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
         <v>105</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>106</v>
       </c>
     </row>

--- a/data/gravel/3T Racemax Italia 2025.xlsx
+++ b/data/gravel/3T Racemax Italia 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{735E28CF-BC39-9844-881F-1C83BF600AC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE1769A4-11DF-AA47-AA9F-580C95474EB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3880" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1152,20 +1152,16 @@
         <v>27</v>
       </c>
       <c r="C31">
-        <f>C33</f>
         <v>157</v>
       </c>
       <c r="D31">
-        <f>AVERAGE(D33,C34)</f>
-        <v>169.5</v>
+        <v>168</v>
       </c>
       <c r="E31">
-        <f t="shared" ref="E31:F31" si="0">AVERAGE(E33,D34)</f>
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F31">
-        <f t="shared" si="0"/>
-        <v>184.5</v>
+        <v>183</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -1173,100 +1169,72 @@
         <v>28</v>
       </c>
       <c r="C32">
-        <f>D31</f>
-        <v>169.5</v>
+        <v>171</v>
       </c>
       <c r="D32">
-        <f t="shared" ref="D32:E32" si="1">E31</f>
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E32">
-        <f t="shared" si="1"/>
-        <v>184.5</v>
+        <v>186</v>
       </c>
       <c r="F32">
-        <f t="shared" ref="F32" si="2">F34</f>
         <v>195</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
-      <c r="C33">
-        <v>157</v>
-      </c>
-      <c r="D33">
-        <v>168</v>
-      </c>
-      <c r="E33">
-        <v>176</v>
-      </c>
-      <c r="F33">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+    <row r="33" spans="1:7" ht="21">
+      <c r="C33" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="21">
       <c r="A34" t="s">
         <v>29</v>
       </c>
       <c r="B34" t="s">
         <v>30</v>
       </c>
-      <c r="C34">
-        <v>171</v>
-      </c>
-      <c r="D34">
-        <v>180</v>
-      </c>
-      <c r="E34">
-        <v>186</v>
-      </c>
-      <c r="F34">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="21">
+      <c r="C34" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>98</v>
       </c>
       <c r="B35" t="s">
         <v>99</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="21">
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>100</v>
       </c>
       <c r="B36" t="s">
         <v>101</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:7">
